--- a/benchmark/generated_files/RIC-3_M_022.xlsx
+++ b/benchmark/generated_files/RIC-3_M_022.xlsx
@@ -433,56 +433,56 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Divisa: EUR</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Filiale: SEDE CENTRALE</t>
+          <t>Tipo conto: Carta ricaricabile</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Tipo conto: Carta ricaricabile</t>
+          <t>Intestatario: Laura Bianchi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Banca: Revolut</t>
+          <t>IBAN: LT12 3456 7890 1234 5678</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Intestatario: Laura Bianchi</t>
+          <t>Saldo iniziale: 5.841,19 EUR</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Periodo: 01/01/2026 - 28/02/2026</t>
+          <t>Movimenti al 28/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Divisa: EUR</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Movimenti al 28/02/2026</t>
+          <t>Codice cliente: 343089</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>IBAN: LT12 3456 7890 1234 5678</t>
+          <t>Periodo: 01/01/2026 - 28/02/2026</t>
         </is>
       </c>
     </row>
@@ -519,11 +519,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 8,42 EUR DEL 01.01.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8189 PAM</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>8.42</v>
+        <v>59.98</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -533,15 +533,15 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>46024</v>
+        <v>46025</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2971 TRATTORIA LA PERGOLA</t>
+          <t>Addebito SDD - SPOTIFY AB</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>72.19</v>
+        <v>11.14</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -551,15 +551,15 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:211264460 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>Pagam. POS - PAGAMENTO POS 10,65 EUR DEL 04.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>94.43000000000001</v>
+        <v>10.65</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -569,15 +569,15 @@
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>46025</v>
+        <v>46026</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9292 IKEA BISTRO NAPOLI</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>14.92</v>
+        <v>50.42</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -587,15 +587,15 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>62.15</v>
+          <t>Bonif. v/fav. - RIF:216874750 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>179.85</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -605,15 +605,15 @@
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>46026</v>
+        <v>46027</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9207 TRATTORIA LA PERGOLA</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>30.15</v>
+          <t>Bonif. v/fav. - RIF:217345146 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>63.79</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -623,15 +623,15 @@
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213797753 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>141.75</v>
+          <t>Pagam. POS - PAGAMENTO POS 77,07 EUR DEL 06.01.2026 A (ITA) WYCON COSMETICS</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>77.06999999999999</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -641,15 +641,15 @@
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 87,62 EUR DEL 07.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4563 LIDL ITALIA</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>87.62</v>
+        <v>159.27</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -659,15 +659,15 @@
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 22,52 EUR DEL 07.01.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>22.52</v>
+        <v>68.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -681,11 +681,11 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 8081 TRATTORIA LA PERGOLA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 9425 STROILI ORO SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>76.53</v>
+        <v>55.06</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -695,15 +695,15 @@
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>46031</v>
+        <v>46030</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 138,98 EUR DEL 09.01.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>138.98</v>
+          <t>Bonif. v/fav. - RIF:217037085 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>188.47</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -713,15 +713,15 @@
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>46031</v>
+        <v>46033</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 24,88 EUR DEL 09.01.2026 A (ITA) BAR CENTRALE</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>24.88</v>
+          <t>Bonif. v/fav. - RIF:213524697 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>220.78</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -731,15 +731,15 @@
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>46032</v>
+        <v>46034</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
+          <t>Disposizione - RIF:211281962 BEN. DR VERDI ODONTOIATRA</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>14.01</v>
+        <v>98.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -749,15 +749,15 @@
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>46032</v>
+        <v>46035</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 12,03 EUR DEL 13.01.2026 A (ITA) UNIEURO S.P.A.</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57.22</v>
+        <v>12.03</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -767,15 +767,15 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>46032</v>
+        <v>46035</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 10,80 EUR DEL 10.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5971 SALMOIRAGHI &amp; VIGANÒ</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>10.8</v>
+        <v>15.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -785,15 +785,15 @@
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>46032</v>
+        <v>46037</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 29,95 EUR DEL 10.01.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6402 IL PANE QUOTIDIANO SESTO SAN GIOVANNI</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>29.95</v>
+        <v>69.48</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -803,15 +803,15 @@
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>46033</v>
+        <v>46037</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 6929 OVS S.P.A.</t>
+          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>96.48999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -821,15 +821,15 @@
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>46033</v>
+        <v>46038</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 29,91 EUR DEL 11.01.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 64,68 EUR DEL 16.01.2026 A (ITA) DECATHLON ASSAGO</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>29.91</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -839,15 +839,15 @@
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>46033</v>
+        <v>46038</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 78,36 EUR DEL 11.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 30,89 EUR DEL 16.01.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>78.36</v>
+        <v>30.89</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -857,15 +857,15 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>46033</v>
+        <v>46039</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217464758 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>209.05</v>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7129 JULIUS MEINL ROZZANO</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>13.31</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -875,15 +875,15 @@
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>46034</v>
+        <v>46039</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 46,92 EUR DEL 12.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 80,63 EUR DEL 17.01.2026 A (ITA) WYCON COSMETICS</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>46.92</v>
+        <v>80.63</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -893,15 +893,15 @@
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>46035</v>
+        <v>46039</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 3576 OVS S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5325 TACO BELL OSTIENSE</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>111.47</v>
+        <v>51.41</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -911,15 +911,15 @@
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>46035</v>
+        <v>46040</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5075 CONAD SUPERSTORE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1366 SALMOIRAGHI &amp; VIGANÒ</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>145.31</v>
+        <v>77.83</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -929,15 +929,15 @@
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 50,36 EUR DEL 15.01.2026 A (ITA) MACELLERIA BONI</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8796 FLOWER BURGER</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50.36</v>
+        <v>54.59</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -947,15 +947,15 @@
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 80,77 EUR DEL 15.01.2026 A (ITA) CONAD CITY ROMA</t>
+          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>80.77</v>
+        <v>86.89</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -965,15 +965,15 @@
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>46037</v>
+        <v>46040</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 61,81 EUR DEL 15.01.2026 A (ITA) PESCHERIA DEL PORTO</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>61.81</v>
+          <t>Bonif. v/fav. - RIF:219730282 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>239.55</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -983,15 +983,15 @@
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>46038</v>
+        <v>46041</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 11,92 EUR DEL 16.01.2026 A (ITA) MEDIAWORLD CARUGATE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2930 PARAFARMACIA CONAD CORSICO</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>11.92</v>
+        <v>242.92</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1001,15 +1001,15 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-212787770</t>
+          <t>Pagam. POS - PAGAMENTO POS 61,88 EUR DEL 20.01.2026 A (ITA) OTTICA AVANZI</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>13.62</v>
+        <v>61.88</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1019,15 +1019,15 @@
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>46039</v>
+        <v>46042</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 1334 POKE HOUSE CENTRO COMM. IL LEONE</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>20.84</v>
+        <v>13.74</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1037,15 +1037,15 @@
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>46040</v>
+        <v>46043</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:211170387 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D43" t="n">
-        <v>99.5</v>
+          <t>Pagam. POS - PAGAMENTO POS 80,34 EUR DEL 21.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>80.34</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1055,15 +1055,15 @@
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-210611999</t>
+          <t>Pagam. POS - PAGAMENTO POS 136,89 EUR DEL 22.01.2026 A (ITA) TIGRE AMICO</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>10.89</v>
+        <v>136.89</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -1073,15 +1073,15 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>46041</v>
+        <v>46044</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:213698444 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D45" t="n">
-        <v>292.21</v>
+          <t>Pagam. POS - PAGAMENTO POS 166,63 EUR DEL 22.01.2026 A (ITA) FAMILA</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>166.63</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -1091,15 +1091,15 @@
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 23,54 EUR DEL 20.01.2026 A (ITA) PANIFICIO TOSI</t>
+          <t>Pagam. POS - PAGAMENTO POS 95,50 EUR DEL 22.01.2026 A (ITA) ARCAPLANET GENOVA</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>23.54</v>
+        <v>95.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -1109,15 +1109,15 @@
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Addebito SDD - WIND TRE S.P.A. MOBILE</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3000 PRIMADONNA</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>97.20999999999999</v>
+        <v>138.97</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1127,15 +1127,15 @@
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>46042</v>
+        <v>46046</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 52,50 EUR DEL 24.01.2026 A (ITA) FRANCO MANCA</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>23.04</v>
+        <v>52.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -1145,15 +1145,15 @@
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>46042</v>
+        <v>46046</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212428462 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D49" t="n">
-        <v>88.81999999999999</v>
+          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>59.94</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -1163,15 +1163,15 @@
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>46042</v>
+        <v>46046</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216059233 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D50" t="n">
-        <v>59.64</v>
+          <t>Pagam. POS - PAGAMENTO POS 84,29 EUR DEL 24.01.2026 A (ITA) CADDY'S PORTA NUOVA</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>84.29000000000001</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -1181,15 +1181,15 @@
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>46044</v>
+        <v>46047</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 47,32 EUR DEL 22.01.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 166,48 EUR DEL 25.01.2026 A (ITA) ARD DISCOUNT</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>47.32</v>
+        <v>166.48</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -1199,15 +1199,15 @@
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>46045</v>
+        <v>46047</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
-        <v>21.26</v>
+          <t>Bonif. v/fav. - RIF:219886135 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>174.25</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1217,15 +1217,15 @@
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 43,63 EUR DEL 23.01.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 178,88 EUR DEL 26.01.2026 A (ITA) MERCATÒ MILANO</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>43.63</v>
+        <v>178.88</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -1235,15 +1235,15 @@
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 32,15 EUR DEL 23.01.2026 A (ITA) OTTICA AVANZI</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>32.15</v>
+          <t>Bonif. v/fav. - RIF:216074314 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>270.28</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1253,15 +1253,15 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>46047</v>
+        <v>46049</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217620212 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>56.13</v>
+          <t>Pagam. POS - PAGAMENTO POS 20,93 EUR DEL 27.01.2026 A (ITA) COMPRO ORO PERUGIA</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>20.93</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -1271,15 +1271,15 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 34,52 EUR DEL 26.01.2026 A (ITA) TABACCHERIA N.12</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>34.52</v>
+          <t>Bonif. v/fav. - RIF:218585506 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>165.33</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -1289,15 +1289,15 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-216229979</t>
+          <t>Pagam. POS - PAGAMENTO POS 70,24 EUR DEL 28.01.2026 A (ITA) VITALDENT CORSICO</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>8.050000000000001</v>
+        <v>70.23999999999999</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -1307,15 +1307,15 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 34,51 EUR DEL 28.01.2026 A (ITA) VALMANO LINGOTTO</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>64.95</v>
+        <v>34.51</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -1325,15 +1325,15 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 9776 OVS S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 33,04 EUR DEL 28.01.2026 A (ITA) RISTORANTE DA GINO</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>145.53</v>
+        <v>33.04</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -1343,15 +1343,15 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 5,67 EUR DEL 28.01.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 118,07 EUR DEL 30.01.2026 A (ITA) GRANDVISION</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>5.67</v>
+        <v>118.07</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -1361,15 +1361,15 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 139,73 EUR DEL 29.01.2026 A (ITA) FARMACIA DR ROSSI</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>139.73</v>
+          <t>Bonif. v/fav. - RIF:215014641 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>254.41</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -1383,11 +1383,11 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>37.53</v>
+          <t>Bonif. v/fav. - RIF:213441352 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>239.22</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -1397,15 +1397,15 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>46052</v>
+        <v>46053</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 46,26 EUR DEL 30.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>Pagam. POS - PAGAMENTO POS 60,12 EUR DEL 31.01.2026 A (ITA) SPIZZICO VENEZIA</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>46.26</v>
+        <v>60.12</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -1415,15 +1415,15 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>46053</v>
+        <v>46054</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 3612 OVS S.P.A.</t>
+          <t>Pagam. POS - PAGAMENTO POS 88,30 EUR DEL 01.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>91.39</v>
+        <v>88.3</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -1433,15 +1433,15 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 107,96 EUR DEL 31.01.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2425 DENTALPRO</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>107.96</v>
+        <v>177.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -1451,15 +1451,15 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>46053</v>
+        <v>46055</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 26,07 EUR DEL 31.01.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5300 DOPPIO MALTO VOMERO</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>26.07</v>
+        <v>12.82</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -1469,15 +1469,15 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>46057</v>
+        <v>46055</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 5789 LIDL ITALIA</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8679 CONAD SUPERSTORE</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>164.27</v>
+        <v>90.84999999999999</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -1487,15 +1487,15 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>46058</v>
+        <v>46055</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 66,07 EUR DEL 05.02.2026 A (ITA) MACELLERIA BONI</t>
+          <t>Pagam. POS - PAGAMENTO POS 76,49 EUR DEL 02.02.2026 A (ITA) CALZEDONIA GROUP</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>66.06999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -1505,15 +1505,15 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>46058</v>
+        <v>46056</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 7820 ESSELUNGA S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8857 TUODÌ CENTRO COMMERCIALE LE GRANGE</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>73.64</v>
+        <v>56.29</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -1523,15 +1523,15 @@
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>46059</v>
+        <v>46056</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Pagam. POS - PAGAMENTO POS 72,64 EUR DEL 03.02.2026 A (ITA) FRANCO MANCA</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>39.42</v>
+        <v>72.64</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -1541,15 +1541,15 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 6292 ESSELUNGA S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 4776 ESSELUNGA S.P.A.</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>100.66</v>
+        <v>44.88</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -1559,15 +1559,15 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 65,12 EUR DEL 06.02.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 23,98 EUR DEL 04.02.2026 A (ITA) UDON</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>65.12</v>
+        <v>23.98</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -1577,15 +1577,15 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>46059</v>
+        <v>46057</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Addebito SDD - SPOTIFY AB</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 3657 ARCAPLANET</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>14.61</v>
+        <v>13.81</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -1595,15 +1595,15 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>46059</v>
+        <v>46058</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216482581 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>248.1</v>
+          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>18.18</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -1613,15 +1613,15 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>46060</v>
+        <v>46058</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 2765 OVS S.P.A.</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6614 ARCAPLANET</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>120.67</v>
+        <v>82.31</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -1631,15 +1631,15 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>46061</v>
+        <v>46060</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 36,36 EUR DEL 08.02.2026 A (ITA) ESSELUNGA MILANO</t>
+          <t>Pagam. POS - PAGAMENTO POS 13,29 EUR DEL 07.02.2026 A (ITA) BAR CENTRALE</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>36.36</v>
+        <v>13.29</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -1653,11 +1653,11 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 17,30 EUR DEL 08.02.2026 A (ITA) RISTORANTE DA GINO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 7697 LIDL ITALIA</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>17.3</v>
+        <v>126.83</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -1667,15 +1667,15 @@
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>46062</v>
+        <v>46061</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 33,56 EUR DEL 09.02.2026 A (ITA) ZARA ITALIA SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 88,51 EUR DEL 08.02.2026 A (ITA) LIDL ITALIA SRL</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>33.56</v>
+        <v>88.51000000000001</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -1685,15 +1685,15 @@
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Addebito SDD - JUST EAT ITALY SRL</t>
+          <t>Pagam. POS - PAGAMENTO POS 106,50 EUR DEL 09.02.2026 A (ITA) ZARA ITALIA SRL</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>77.68000000000001</v>
+        <v>106.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -1703,15 +1703,15 @@
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>46063</v>
+        <v>46062</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AMAZON.IT MARKETPLACE - ORDINE 402-212488203</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>14.74</v>
+          <t>Bonif. v/fav. - RIF:217654021 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>270.79</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -1721,15 +1721,15 @@
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>46064</v>
+        <v>46063</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 76,45 EUR DEL 11.02.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Pagam. POS - PAGAMENTO POS 57,75 EUR DEL 10.02.2026 A (ITA) BLUESPIRIT MESTRE</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>76.45</v>
+        <v>57.75</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -1743,11 +1743,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>PRELIEVO ATM BANCOMAT FIL. 00456 MILANO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 2633 SPORTLER SAN GIULIANO MILANESE</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9.09</v>
+        <v>101.87</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -1761,11 +1761,11 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>PAGAMENTO CONTACTLESS CARTA **** 8330 CONAD SUPERSTORE</t>
+          <t>Pagam. POS - PAGAMENTO POS 29,93 EUR DEL 12.02.2026 A (ITA) ALE-HOP COLOGNO MONZESE</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>170.31</v>
+        <v>29.93</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -1779,11 +1779,11 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:218157115 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>272.1</v>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 6726 DESPAR</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>62.02</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -1793,15 +1793,15 @@
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>46066</v>
+        <v>46065</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Addebito SDD - APPLE.COM/BILL</t>
+          <t>Addebito SDD - GOOGLE *CLOUD STORAGE</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>10.74</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -1811,15 +1811,15 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>46067</v>
+        <v>46065</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 8,31 EUR DEL 14.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
+          <t>Pagam. POS - PAGAMENTO POS 84,84 EUR DEL 12.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>8.31</v>
+        <v>84.84</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -1829,15 +1829,15 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>46067</v>
+        <v>46065</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 37,94 EUR DEL 14.02.2026 A (ITA) COOP LOMBARDIA</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>37.94</v>
+          <t>Bonif. v/fav. - RIF:212817316 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>151.72</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -1847,15 +1847,15 @@
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>46067</v>
+        <v>46066</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:219130493 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>112.77</v>
+          <t>Pagam. POS - PAGAMENTO POS 126,33 EUR DEL 13.02.2026 A (ITA) CARREFOUR CONTACT VERONA</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>126.33</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -1865,15 +1865,15 @@
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>46068</v>
+        <v>46066</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 12,98 EUR DEL 15.02.2026 A (ITA) ROSTICCERIA DA MARIO</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>12.98</v>
+          <t>Bonif. v/fav. - RIF:215853147 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>182.11</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -1887,11 +1887,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Addebito SDD - NETFLIX INTERNATIONAL B.V.</t>
+          <t>Pagam. POS - PAGAMENTO POS 58,11 EUR DEL 15.02.2026 A (ITA) CHURCH'S</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9.32</v>
+        <v>58.11</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -1905,11 +1905,11 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Disposizione - RIF:210309179 BEN. TINTORIA RAPIDA CENTRO</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 5391 TACO BELL</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>50.3</v>
+        <v>66.75</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -1923,11 +1923,11 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:217742508 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>111.08</v>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8945 TRATTORIA LA PERGOLA</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>28.84</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -1937,15 +1937,15 @@
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>46070</v>
+        <v>46069</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Addebito SDD - TELECOM ITALIA S.P.A. FIBRA</t>
+          <t>Addebito SDD - APPLE.COM/BILL</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>10.81</v>
+        <v>5.02</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -1959,11 +1959,11 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>Addebito SDD - JUST EAT ITALY SRL</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>22.86</v>
+        <v>43.88</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -1973,15 +1973,15 @@
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>46073</v>
+        <v>46070</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 96,44 EUR DEL 20.02.2026 A (ITA) CENTRO DIAGNOSTICO SAN DONATO</t>
+          <t>Pagam. POS - PAGAMENTO POS 12,74 EUR DEL 17.02.2026 A (ITA) MAXI ZOO FUORIGROTTA</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>96.44</v>
+        <v>12.74</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -1991,15 +1991,15 @@
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>46074</v>
+        <v>46071</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 42,42 EUR DEL 21.02.2026 A (ITA) MCDONALD'S ITALIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 65,70 EUR DEL 18.02.2026 A (ITA) IKEA BISTRO</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>42.42</v>
+        <v>65.7</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -2009,15 +2009,15 @@
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>46075</v>
+        <v>46071</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 90,02 EUR DEL 22.02.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 73,99 EUR DEL 18.02.2026 A (ITA) JULIUS MEINL</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>90.02</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -2027,15 +2027,15 @@
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>46076</v>
+        <v>46072</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Addebito SDD - GENERALI ITALIA POLIZZA VITA</t>
+          <t>Pagam. POS - PAGAMENTO POS 123,95 EUR DEL 19.02.2026 A (ITA) IKEA SWEDISH FOOD MARKET LINGOTTO</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>30.52</v>
+        <v>123.95</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -2045,15 +2045,15 @@
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>46076</v>
+        <v>46072</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:212100416 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>253.65</v>
+          <t>Pagam. POS - PAGAMENTO POS 37,19 EUR DEL 19.02.2026 A (ITA) AUTOGRILL CINISELLO BALSAMO</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>37.19</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -2063,15 +2063,15 @@
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>46077</v>
+        <v>46073</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 146,68 EUR DEL 24.02.2026 A (ITA) H&amp;M HENNES AND MAURITZ</t>
+          <t>Pagam. POS - PAGAMENTO POS 21,32 EUR DEL 20.02.2026 A (ITA) RISTORANTE DA GINO</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>146.68</v>
+        <v>21.32</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -2081,15 +2081,15 @@
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>46077</v>
+        <v>46074</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Addebito SDD - DELIVEROO ITALY SRL</t>
+          <t>PAGAMENTO CONTACTLESS CARTA **** 8781 IKEA RESTAURANT</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>44.89</v>
+        <v>49.13</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -2099,15 +2099,15 @@
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>46077</v>
+        <v>46074</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 22,07 EUR DEL 24.02.2026 A (ITA) COOP LOMBARDIA</t>
+          <t>Pagam. POS - PAGAMENTO POS 52,43 EUR DEL 21.02.2026 A (ITA) PIZZERIA NAPOLI</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>22.07</v>
+        <v>52.43</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -2117,15 +2117,15 @@
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>46077</v>
+        <v>46074</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:215734553 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>128.01</v>
+          <t>Pagam. POS - PAGAMENTO POS 40,87 EUR DEL 21.02.2026 A (ITA) COOP LOMBARDIA</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>40.87</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -2135,15 +2135,15 @@
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>46079</v>
+        <v>46075</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 116,45 EUR DEL 26.02.2026 A (ITA) DECATHLON ASSAGO</t>
+          <t>Pagam. POS - PAGAMENTO POS 33,31 EUR DEL 22.02.2026 A (ITA) COOP LOMBARDIA</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>116.45</v>
+        <v>33.31</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -2153,15 +2153,15 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>46081</v>
+        <v>46076</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 50,65 EUR DEL 28.02.2026 A (ITA) TABACCHERIA N.12</t>
+          <t>Pagam. POS - PAGAMENTO POS 69,50 EUR DEL 23.02.2026 A (ITA) ACQUA &amp; SAPONE NAPOLI</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>50.65</v>
+        <v>69.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -2171,15 +2171,15 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>46081</v>
+        <v>46076</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Pagam. POS - PAGAMENTO POS 56,94 EUR DEL 28.02.2026 A (ITA) MERCATO RIONALE PORTA PALAZZO</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>56.94</v>
+          <t>Bonif. v/fav. - RIF:210859412 ORD. RICARICA REVOLUT LAURA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>76.3</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -2189,15 +2189,15 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>46081</v>
+        <v>46076</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:216379687 ORD. RICARICA REVOLUT LAURA</t>
+          <t>Bonif. v/fav. - RIF:219900784 ORD. RICARICA REVOLUT LAURA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>223.86</v>
+        <v>144.74</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -2211,11 +2211,11 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bonif. v/fav. - RIF:214169748 ORD. RICARICA REVOLUT LAURA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>247</v>
+          <t>Pagam. POS - PAGAMENTO POS 168,45 EUR DEL 28.02.2026 A (ITA) IPERCOOP ROZZANO</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>168.45</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
